--- a/artfynd/A 25683-2023 artfynd.xlsx
+++ b/artfynd/A 25683-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25683-2023 artfynd.xlsx
+++ b/artfynd/A 25683-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3015,6 +3015,486 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121466756</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56252</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nyängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>588077</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6616018</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hubbo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121466755</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56256</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Dokumentation efterfrågas</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100087</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fransfladdermus</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Myotis nattereri</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nyängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>588077</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6616018</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hubbo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121466754</v>
+      </c>
+      <c r="B25" t="n">
+        <v>56259</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nyängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>588077</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6616018</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hubbo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121466758</v>
+      </c>
+      <c r="B26" t="n">
+        <v>56245</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nyängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>588077</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6616018</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hubbo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25683-2023 artfynd.xlsx
+++ b/artfynd/A 25683-2023 artfynd.xlsx
@@ -3137,42 +3137,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121466755</v>
+        <v>121466754</v>
       </c>
       <c r="B24" t="n">
-        <v>56256</v>
+        <v>56259</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100087</v>
+        <v>100092</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3257,42 +3257,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121466754</v>
+        <v>121466755</v>
       </c>
       <c r="B25" t="n">
-        <v>56259</v>
+        <v>56256</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100092</v>
+        <v>100087</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">

--- a/artfynd/A 25683-2023 artfynd.xlsx
+++ b/artfynd/A 25683-2023 artfynd.xlsx
@@ -3017,32 +3017,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121466756</v>
+        <v>121466755</v>
       </c>
       <c r="B23" t="n">
-        <v>56252</v>
+        <v>56256</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205992</v>
+        <v>100087</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3137,10 +3137,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121466754</v>
+        <v>121466758</v>
       </c>
       <c r="B24" t="n">
-        <v>56259</v>
+        <v>56245</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3149,30 +3149,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3257,42 +3257,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121466755</v>
+        <v>121466754</v>
       </c>
       <c r="B25" t="n">
-        <v>56256</v>
+        <v>56259</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100087</v>
+        <v>100092</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3377,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121466758</v>
+        <v>121466756</v>
       </c>
       <c r="B26" t="n">
-        <v>56245</v>
+        <v>56252</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,30 +3389,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">

--- a/artfynd/A 25683-2023 artfynd.xlsx
+++ b/artfynd/A 25683-2023 artfynd.xlsx
@@ -3017,14 +3017,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121466755</v>
+        <v>121466758</v>
       </c>
       <c r="B23" t="n">
-        <v>56256</v>
+        <v>56248</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3033,26 +3033,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100087</v>
+        <v>205998</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3137,10 +3137,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121466758</v>
+        <v>121466754</v>
       </c>
       <c r="B24" t="n">
-        <v>56245</v>
+        <v>56262</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3149,30 +3149,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3257,42 +3257,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121466754</v>
+        <v>121466755</v>
       </c>
       <c r="B25" t="n">
         <v>56259</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100092</v>
+        <v>100087</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3380,7 +3380,7 @@
         <v>121466756</v>
       </c>
       <c r="B26" t="n">
-        <v>56252</v>
+        <v>56255</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 25683-2023 artfynd.xlsx
+++ b/artfynd/A 25683-2023 artfynd.xlsx
@@ -3257,32 +3257,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121466755</v>
+        <v>121466756</v>
       </c>
       <c r="B25" t="n">
-        <v>56259</v>
+        <v>56255</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100087</v>
+        <v>205992</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3377,32 +3377,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121466756</v>
+        <v>121466755</v>
       </c>
       <c r="B26" t="n">
-        <v>56255</v>
+        <v>56259</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205992</v>
+        <v>100087</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">

--- a/artfynd/A 25683-2023 artfynd.xlsx
+++ b/artfynd/A 25683-2023 artfynd.xlsx
@@ -3017,14 +3017,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121466758</v>
+        <v>121466755</v>
       </c>
       <c r="B23" t="n">
-        <v>56248</v>
+        <v>56260</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3033,26 +3033,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205998</v>
+        <v>100087</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3140,7 +3140,7 @@
         <v>121466754</v>
       </c>
       <c r="B24" t="n">
-        <v>56262</v>
+        <v>56263</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121466756</v>
+        <v>121466758</v>
       </c>
       <c r="B25" t="n">
-        <v>56255</v>
+        <v>56249</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3269,30 +3269,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3377,32 +3377,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121466755</v>
+        <v>121466756</v>
       </c>
       <c r="B26" t="n">
-        <v>56259</v>
+        <v>56256</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100087</v>
+        <v>205992</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">

--- a/artfynd/A 25683-2023 artfynd.xlsx
+++ b/artfynd/A 25683-2023 artfynd.xlsx
@@ -3017,42 +3017,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121466755</v>
+        <v>121466754</v>
       </c>
       <c r="B23" t="n">
-        <v>56260</v>
+        <v>56264</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100087</v>
+        <v>100092</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3137,42 +3137,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121466754</v>
+        <v>121466755</v>
       </c>
       <c r="B24" t="n">
-        <v>56263</v>
+        <v>56261</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100092</v>
+        <v>100087</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3260,7 +3260,7 @@
         <v>121466758</v>
       </c>
       <c r="B25" t="n">
-        <v>56249</v>
+        <v>56250</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>121466756</v>
       </c>
       <c r="B26" t="n">
-        <v>56256</v>
+        <v>56257</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 25683-2023 artfynd.xlsx
+++ b/artfynd/A 25683-2023 artfynd.xlsx
@@ -3137,32 +3137,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121466755</v>
+        <v>121466756</v>
       </c>
       <c r="B24" t="n">
-        <v>56261</v>
+        <v>56257</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100087</v>
+        <v>205992</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3257,14 +3257,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121466758</v>
+        <v>121466755</v>
       </c>
       <c r="B25" t="n">
-        <v>56250</v>
+        <v>56261</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3273,26 +3273,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205998</v>
+        <v>100087</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3377,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121466756</v>
+        <v>121466758</v>
       </c>
       <c r="B26" t="n">
-        <v>56257</v>
+        <v>56250</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,30 +3389,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">

--- a/artfynd/A 25683-2023 artfynd.xlsx
+++ b/artfynd/A 25683-2023 artfynd.xlsx
@@ -3017,10 +3017,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121466754</v>
+        <v>121466758</v>
       </c>
       <c r="B23" t="n">
-        <v>56264</v>
+        <v>56250</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3029,30 +3029,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3137,32 +3137,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121466756</v>
+        <v>121466755</v>
       </c>
       <c r="B24" t="n">
-        <v>56257</v>
+        <v>56261</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205992</v>
+        <v>100087</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3257,42 +3257,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121466755</v>
+        <v>121466754</v>
       </c>
       <c r="B25" t="n">
-        <v>56261</v>
+        <v>56264</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100087</v>
+        <v>100092</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3377,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121466758</v>
+        <v>121466756</v>
       </c>
       <c r="B26" t="n">
-        <v>56250</v>
+        <v>56257</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,30 +3389,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">

--- a/artfynd/A 25683-2023 artfynd.xlsx
+++ b/artfynd/A 25683-2023 artfynd.xlsx
@@ -3017,14 +3017,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121466758</v>
+        <v>121466755</v>
       </c>
       <c r="B23" t="n">
-        <v>56250</v>
+        <v>56261</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3033,26 +3033,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205998</v>
+        <v>100087</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3137,42 +3137,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121466755</v>
+        <v>121466754</v>
       </c>
       <c r="B24" t="n">
-        <v>56261</v>
+        <v>56264</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100087</v>
+        <v>100092</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121466754</v>
+        <v>121466756</v>
       </c>
       <c r="B25" t="n">
-        <v>56264</v>
+        <v>56257</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3273,26 +3273,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3377,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121466756</v>
+        <v>121466758</v>
       </c>
       <c r="B26" t="n">
-        <v>56257</v>
+        <v>56250</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,30 +3389,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">

--- a/artfynd/A 25683-2023 artfynd.xlsx
+++ b/artfynd/A 25683-2023 artfynd.xlsx
@@ -3017,42 +3017,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121466754</v>
+        <v>121466755</v>
       </c>
       <c r="B23" t="n">
-        <v>56265</v>
+        <v>56262</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100092</v>
+        <v>100087</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3137,10 +3137,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121466756</v>
+        <v>121466758</v>
       </c>
       <c r="B24" t="n">
-        <v>56258</v>
+        <v>56251</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3149,30 +3149,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3257,32 +3257,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121466755</v>
+        <v>121466756</v>
       </c>
       <c r="B25" t="n">
-        <v>56262</v>
+        <v>56258</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100087</v>
+        <v>205992</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3377,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121466758</v>
+        <v>121466754</v>
       </c>
       <c r="B26" t="n">
-        <v>56251</v>
+        <v>56265</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,30 +3389,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">

--- a/artfynd/A 25683-2023 artfynd.xlsx
+++ b/artfynd/A 25683-2023 artfynd.xlsx
@@ -3017,14 +3017,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121466755</v>
+        <v>121466758</v>
       </c>
       <c r="B23" t="n">
-        <v>56262</v>
+        <v>56251</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3033,26 +3033,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100087</v>
+        <v>205998</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3137,14 +3137,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121466758</v>
+        <v>121466755</v>
       </c>
       <c r="B24" t="n">
-        <v>56251</v>
+        <v>56262</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3153,26 +3153,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205998</v>
+        <v>100087</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121466756</v>
+        <v>121466754</v>
       </c>
       <c r="B25" t="n">
-        <v>56258</v>
+        <v>56265</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3273,26 +3273,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3377,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121466754</v>
+        <v>121466756</v>
       </c>
       <c r="B26" t="n">
-        <v>56265</v>
+        <v>56258</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3393,26 +3393,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">

--- a/artfynd/A 25683-2023 artfynd.xlsx
+++ b/artfynd/A 25683-2023 artfynd.xlsx
@@ -3140,12 +3140,7 @@
         <v>121466755</v>
       </c>
       <c r="B24" t="n">
-        <v>56262</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Dokumentation efterfrågas</t>
-        </is>
+        <v>56739</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 25683-2023 artfynd.xlsx
+++ b/artfynd/A 25683-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96753480</v>
+        <v>96753467</v>
       </c>
       <c r="B2" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>200m O Bergtäkten, Vstm</t>
+          <t>Ca 700m V Nyängen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587936.2309676831</v>
+        <v>587959</v>
       </c>
       <c r="R2" t="n">
-        <v>6615979.055937049</v>
+        <v>6615983</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +765,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -787,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96753476</v>
+        <v>96859198</v>
       </c>
       <c r="B3" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587940.1000221415</v>
+        <v>587943</v>
       </c>
       <c r="R3" t="n">
-        <v>6615986.726789031</v>
+        <v>6615980</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +845,14 @@
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,62 +867,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Anna Koffman, Petter Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96753479</v>
+        <v>96859199</v>
       </c>
       <c r="B4" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>200m O Bergtäkten, Vstm</t>
+          <t>Ca 700m V Nyängen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588089.3305600542</v>
+        <v>587944</v>
       </c>
       <c r="R4" t="n">
-        <v>6615775.9780677</v>
+        <v>6615984</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +969,7 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1011,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96753478</v>
+        <v>96859269</v>
       </c>
       <c r="B5" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>200m O Bergtäkten, Vstm</t>
+          <t>Ca 700m V Nyängen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588088.2180198078</v>
+        <v>587959</v>
       </c>
       <c r="R5" t="n">
-        <v>6615887.632714933</v>
+        <v>6615983</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,27 +1046,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>Gammla fruktkroppar på granlåga tillsammans med murkna klibbtickor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1071,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1128,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96753477</v>
+        <v>96859223</v>
       </c>
       <c r="B6" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,37 +1094,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>700m V väg 56, 300m O Tippen, Vstm</t>
+          <t>Ca 700m V Nyängen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587939.1594943394</v>
+        <v>588090</v>
       </c>
       <c r="R6" t="n">
-        <v>6615983.672732322</v>
+        <v>6615776</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,22 +1148,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Uppehåller sig i objektet efter att ha kommit inflygande från norr</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1173,7 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -1240,37 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96753467</v>
+        <v>96859224</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,13 +1220,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587958.9137537086</v>
+        <v>587936</v>
       </c>
       <c r="R7" t="n">
-        <v>6615983.126890638</v>
+        <v>6615979</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,24 +1253,14 @@
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Läte nära</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,7 +1275,7 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -1357,50 +1287,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96753481</v>
+        <v>121466755</v>
       </c>
       <c r="B8" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>100087</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>200m O Bergtäkten, Vstm</t>
+          <t>Nyängen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588088.9375802283</v>
+        <v>588077</v>
       </c>
       <c r="R8" t="n">
-        <v>6615749.690474079</v>
+        <v>6616018</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,27 +1366,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gnag gran</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,65 +1386,78 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96753488</v>
+        <v>121466754</v>
       </c>
       <c r="B9" t="n">
-        <v>57999</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103057</v>
+        <v>100092</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ca 600m S Nyängen, Vstm</t>
+          <t>Nyängen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588108</v>
+        <v>588077</v>
       </c>
       <c r="R9" t="n">
-        <v>6615660</v>
+        <v>6616018</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,17 +1481,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>En rastande fågel</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,65 +1501,78 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ann-Sofie Frydenlund</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96753486</v>
+        <v>121466759</v>
       </c>
       <c r="B10" t="n">
-        <v>57445</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100092</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ca 600m S Nyängen, Vstm</t>
+          <t>Nyängen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587944</v>
+        <v>588209</v>
       </c>
       <c r="R10" t="n">
-        <v>6615984</v>
+        <v>6616147</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,17 +1596,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Två</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,65 +1616,64 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ann-Sofie Frydenlund</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96753485</v>
+        <v>96753474</v>
       </c>
       <c r="B11" t="n">
-        <v>57445</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ca 600m S Nyängen, Vstm</t>
+          <t>Ca 700m V Nyängen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
         <v>587943</v>
       </c>
       <c r="R11" t="n">
-        <v>6615980</v>
+        <v>6615929</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,17 +1697,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera ex i meståg</t>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,44 +1727,39 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96753483</v>
+        <v>96753476</v>
       </c>
       <c r="B12" t="n">
-        <v>57445</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1769,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587939</v>
+        <v>587940</v>
       </c>
       <c r="R12" t="n">
-        <v>6615964</v>
+        <v>6615987</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,50 +1831,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96859199</v>
+        <v>96753477</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ca 700m V Nyängen, Vstm</t>
+          <t>700m V väg 56, 300m O Tippen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587944.2185945489</v>
+        <v>587939</v>
       </c>
       <c r="R13" t="n">
-        <v>6615983.791758995</v>
+        <v>6615984</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,27 +1896,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2002,27 +1916,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96859260</v>
+        <v>96753478</v>
       </c>
       <c r="B14" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,34 +1939,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ca 700m V Nyängen, Vstm</t>
+          <t>200m O Bergtäkten, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588048.5531239476</v>
+        <v>588088</v>
       </c>
       <c r="R14" t="n">
-        <v>6615852.335219868</v>
+        <v>6615888</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,22 +1993,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,27 +2018,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96859259</v>
+        <v>96753479</v>
       </c>
       <c r="B15" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,34 +2041,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ca 700m V Nyängen, Vstm</t>
+          <t>200m O Bergtäkten, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588054.1508985941</v>
+        <v>588090</v>
       </c>
       <c r="R15" t="n">
-        <v>6615636.17522793</v>
+        <v>6615776</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,22 +2095,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2226,27 +2115,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96859262</v>
+        <v>96753480</v>
       </c>
       <c r="B16" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,34 +2138,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ca 700m V Nyängen, Vstm</t>
+          <t>200m O Bergtäkten, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587939.1169768485</v>
+        <v>587936</v>
       </c>
       <c r="R16" t="n">
-        <v>6615963.964132701</v>
+        <v>6615979</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2308,27 +2192,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gnag</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,7 +2212,7 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -2355,15 +2224,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96859269</v>
+        <v>96753481</v>
       </c>
       <c r="B17" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,34 +2235,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>100299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ca 700m V Nyängen, Vstm</t>
+          <t>200m O Bergtäkten, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587958.9137537086</v>
+        <v>588089</v>
       </c>
       <c r="R17" t="n">
-        <v>6615983.126890638</v>
+        <v>6615750</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2425,27 +2289,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gammla fruktkroppar på granlåga tillsammans med murkna klibbtickor</t>
+          <t>Gnag gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2460,7 +2314,7 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2472,37 +2326,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96859198</v>
+        <v>96859258</v>
       </c>
       <c r="B18" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587943.3018341872</v>
+        <v>588031</v>
       </c>
       <c r="R18" t="n">
-        <v>6615979.727613454</v>
+        <v>6615628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2545,24 +2394,9 @@
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,27 +2411,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna Koffman, Petter Andersson</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96859258</v>
+        <v>96859259</v>
       </c>
       <c r="B19" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588031.5612340211</v>
+        <v>588054</v>
       </c>
       <c r="R19" t="n">
-        <v>6615628.062664295</v>
+        <v>6615636</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2662,19 +2491,9 @@
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2689,7 +2508,7 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -2701,37 +2520,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96859215</v>
+        <v>96859260</v>
       </c>
       <c r="B20" t="n">
-        <v>57445</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,13 +2555,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587939</v>
+        <v>588049</v>
       </c>
       <c r="R20" t="n">
-        <v>6615984</v>
+        <v>6615852</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2803,37 +2617,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96859224</v>
+        <v>96859261</v>
       </c>
       <c r="B21" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,13 +2652,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587936</v>
+        <v>587943</v>
       </c>
       <c r="R21" t="n">
-        <v>6615979</v>
+        <v>6615929</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2883,7 +2692,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Läte nära</t>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2910,37 +2719,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96859223</v>
+        <v>96859262</v>
       </c>
       <c r="B22" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,13 +2754,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588090</v>
+        <v>587939</v>
       </c>
       <c r="R22" t="n">
-        <v>6615776</v>
+        <v>6615964</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,7 +2794,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Uppehåller sig i objektet efter att ha kommit inflygande från norr</t>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,22 +2814,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121466758</v>
+        <v>96753483</v>
       </c>
       <c r="B23" t="n">
-        <v>56251</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,51 +2832,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205998</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nyängen, Vstm</t>
+          <t>Ca 700m V Nyängen, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588077</v>
+        <v>587939</v>
       </c>
       <c r="R23" t="n">
-        <v>6616018</v>
+        <v>6615964</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3101,12 +2886,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3121,26 +2906,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
-        </is>
-      </c>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121466755</v>
+        <v>96753485</v>
       </c>
       <c r="B24" t="n">
-        <v>56759</v>
+        <v>58114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3148,51 +2929,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100087</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nyängen, Vstm</t>
+          <t>Ca 600m S Nyängen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588077</v>
+        <v>587943</v>
       </c>
       <c r="R24" t="n">
-        <v>6616018</v>
+        <v>6615980</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3216,12 +2983,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Flera ex i meståg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3236,83 +3008,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
-        </is>
-      </c>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121466754</v>
+        <v>96753486</v>
       </c>
       <c r="B25" t="n">
-        <v>56265</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100092</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nyängen, Vstm</t>
+          <t>Ca 600m S Nyängen, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588077</v>
+        <v>587944</v>
       </c>
       <c r="R25" t="n">
-        <v>6616018</v>
+        <v>6615984</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3336,12 +3085,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Två</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,83 +3110,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
-        </is>
-      </c>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121466756</v>
+        <v>96859215</v>
       </c>
       <c r="B26" t="n">
-        <v>56258</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205992</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nyängen, Vstm</t>
+          <t>Ca 700m V Nyängen, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588077</v>
+        <v>587939</v>
       </c>
       <c r="R26" t="n">
-        <v>6616018</v>
+        <v>6615984</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3456,12 +3187,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3476,15 +3207,458 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
+          <t>Ann-Sofie Frydenlund</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>96753488</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58649</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103057</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sävsparv</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Emberiza schoeniclus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ca 600m S Nyängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>588108</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6615660</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hubbo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>En rastande fågel</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ann-Sofie Frydenlund</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121466756</v>
+      </c>
+      <c r="B28" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nyängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>588077</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6616018</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hubbo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Greensway AB</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>Jannik Jansons</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr">
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121466760</v>
+      </c>
+      <c r="B29" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nyängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>588209</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6616147</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hubbo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121466758</v>
+      </c>
+      <c r="B30" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nyängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>588077</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6616018</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hubbo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
         <is>
           <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
         </is>

--- a/artfynd/A 25683-2023 artfynd.xlsx
+++ b/artfynd/A 25683-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96753467</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96859198</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96859199</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96859269</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96859223</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96859224</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
           <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121466755</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1514,6 +1554,11 @@
           <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121466754</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
           <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121466759</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1731,6 +1781,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96753474</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1828,6 +1883,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96753476</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1925,6 +1985,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96753477</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2027,6 +2092,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96753478</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2124,6 +2194,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96753479</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2221,6 +2296,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96753480</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2323,6 +2403,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96753481</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2420,6 +2505,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96859258</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2517,6 +2607,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96859259</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2614,6 +2709,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96859260</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2716,6 +2816,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96859261</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2818,6 +2923,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96859262</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2915,6 +3025,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96753483</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3017,6 +3132,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96753485</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3119,6 +3239,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96753486</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3216,6 +3341,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96859215</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3318,6 +3448,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96753488</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3433,6 +3568,11 @@
           <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121466756</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3548,6 +3688,11 @@
           <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121466760</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3663,8 +3808,44 @@
           <t>Västerås stad - Fladdermusinventering Tunbytorp</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121466758</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>